--- a/apps/main_app/data/Quan Ly Lop Hoc 2025-2026.xlsx
+++ b/apps/main_app/data/Quan Ly Lop Hoc 2025-2026.xlsx
@@ -7,6 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Danh Sach Lop" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Đợt 2 - 1026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Đợt 1 - 0626" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -581,7 +583,6 @@
           <t>Cơ sở Q9</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>05/2026</t>
@@ -599,7 +600,7 @@
         <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -793,4 +794,274 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mã Lớp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Niên Khóa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tên Lớp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Địa điểm</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Phòng học</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Buổi học</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Lịch học</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Giờ học</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Thời gian khai giảng</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Ngày kết thúc khóa</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SL Min</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>SL Max</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>SL Hiện tại</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LNH1026NGA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh Level 3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cơ sở Q9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tối</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2-4-6</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18:00 - 20:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Dự kiến</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LNH1026NQA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tiếng Anh Level 4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cơ sở Q9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tối</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2-4-6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18:00 - 20:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Dự kiến</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SL Hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>